--- a/report_1.xlsx
+++ b/report_1.xlsx
@@ -9558,7 +9558,7 @@
         <v>40636</v>
       </c>
       <c r="E2" t="n">
-        <v>5494</v>
+        <v>5499</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -9584,7 +9584,7 @@
         <v>41311</v>
       </c>
       <c r="E3" t="n">
-        <v>4819</v>
+        <v>4824</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -9610,7 +9610,7 @@
         <v>41434</v>
       </c>
       <c r="E4" t="n">
-        <v>4696</v>
+        <v>4701</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -9636,7 +9636,7 @@
         <v>41691</v>
       </c>
       <c r="E5" t="n">
-        <v>4439</v>
+        <v>4444</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -9662,7 +9662,7 @@
         <v>41727</v>
       </c>
       <c r="E6" t="n">
-        <v>4403</v>
+        <v>4408</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -9688,7 +9688,7 @@
         <v>41860</v>
       </c>
       <c r="E7" t="n">
-        <v>4270</v>
+        <v>4275</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -9714,7 +9714,7 @@
         <v>41969</v>
       </c>
       <c r="E8" t="n">
-        <v>4161</v>
+        <v>4166</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -9740,7 +9740,7 @@
         <v>42366</v>
       </c>
       <c r="E9" t="n">
-        <v>3764</v>
+        <v>3769</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -9766,7 +9766,7 @@
         <v>42374</v>
       </c>
       <c r="E10" t="n">
-        <v>3756</v>
+        <v>3761</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -9792,7 +9792,7 @@
         <v>42421</v>
       </c>
       <c r="E11" t="n">
-        <v>3709</v>
+        <v>3714</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -9818,7 +9818,7 @@
         <v>42449</v>
       </c>
       <c r="E12" t="n">
-        <v>3681</v>
+        <v>3686</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -9844,7 +9844,7 @@
         <v>42463</v>
       </c>
       <c r="E13" t="n">
-        <v>3667</v>
+        <v>3672</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -9870,7 +9870,7 @@
         <v>42497</v>
       </c>
       <c r="E14" t="n">
-        <v>3633</v>
+        <v>3638</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -9896,7 +9896,7 @@
         <v>42628</v>
       </c>
       <c r="E15" t="n">
-        <v>3502</v>
+        <v>3507</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -9922,7 +9922,7 @@
         <v>42633</v>
       </c>
       <c r="E16" t="n">
-        <v>3497</v>
+        <v>3502</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -9948,7 +9948,7 @@
         <v>42657</v>
       </c>
       <c r="E17" t="n">
-        <v>3473</v>
+        <v>3478</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -9974,7 +9974,7 @@
         <v>42669</v>
       </c>
       <c r="E18" t="n">
-        <v>3461</v>
+        <v>3466</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -10000,7 +10000,7 @@
         <v>42678</v>
       </c>
       <c r="E19" t="n">
-        <v>3452</v>
+        <v>3457</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -10026,7 +10026,7 @@
         <v>42685</v>
       </c>
       <c r="E20" t="n">
-        <v>3445</v>
+        <v>3450</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -10052,7 +10052,7 @@
         <v>42729</v>
       </c>
       <c r="E21" t="n">
-        <v>3401</v>
+        <v>3406</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -10078,7 +10078,7 @@
         <v>42850</v>
       </c>
       <c r="E22" t="n">
-        <v>3280</v>
+        <v>3285</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         <v>42863</v>
       </c>
       <c r="E23" t="n">
-        <v>3267</v>
+        <v>3272</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -10130,7 +10130,7 @@
         <v>42899</v>
       </c>
       <c r="E24" t="n">
-        <v>3231</v>
+        <v>3236</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -10156,7 +10156,7 @@
         <v>42906</v>
       </c>
       <c r="E25" t="n">
-        <v>3224</v>
+        <v>3229</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -10182,7 +10182,7 @@
         <v>42974</v>
       </c>
       <c r="E26" t="n">
-        <v>3156</v>
+        <v>3161</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -10208,7 +10208,7 @@
         <v>43044</v>
       </c>
       <c r="E27" t="n">
-        <v>3086</v>
+        <v>3091</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -10234,7 +10234,7 @@
         <v>43148</v>
       </c>
       <c r="E28" t="n">
-        <v>2982</v>
+        <v>2987</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -10260,7 +10260,7 @@
         <v>43216</v>
       </c>
       <c r="E29" t="n">
-        <v>2914</v>
+        <v>2919</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -10286,7 +10286,7 @@
         <v>43238</v>
       </c>
       <c r="E30" t="n">
-        <v>2892</v>
+        <v>2897</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -10312,7 +10312,7 @@
         <v>43274</v>
       </c>
       <c r="E31" t="n">
-        <v>2856</v>
+        <v>2861</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -10338,7 +10338,7 @@
         <v>43311</v>
       </c>
       <c r="E32" t="n">
-        <v>2819</v>
+        <v>2824</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -10364,7 +10364,7 @@
         <v>43352</v>
       </c>
       <c r="E33" t="n">
-        <v>2778</v>
+        <v>2783</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -10390,7 +10390,7 @@
         <v>43359</v>
       </c>
       <c r="E34" t="n">
-        <v>2771</v>
+        <v>2776</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -10416,7 +10416,7 @@
         <v>43369</v>
       </c>
       <c r="E35" t="n">
-        <v>2761</v>
+        <v>2766</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -10442,7 +10442,7 @@
         <v>43392</v>
       </c>
       <c r="E36" t="n">
-        <v>2738</v>
+        <v>2743</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -10468,7 +10468,7 @@
         <v>43393</v>
       </c>
       <c r="E37" t="n">
-        <v>2737</v>
+        <v>2742</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -10494,7 +10494,7 @@
         <v>43420</v>
       </c>
       <c r="E38" t="n">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -10520,7 +10520,7 @@
         <v>43471</v>
       </c>
       <c r="E39" t="n">
-        <v>2659</v>
+        <v>2664</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -10546,7 +10546,7 @@
         <v>43490</v>
       </c>
       <c r="E40" t="n">
-        <v>2640</v>
+        <v>2645</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -10572,7 +10572,7 @@
         <v>43538</v>
       </c>
       <c r="E41" t="n">
-        <v>2592</v>
+        <v>2597</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -10598,7 +10598,7 @@
         <v>43657</v>
       </c>
       <c r="E42" t="n">
-        <v>2473</v>
+        <v>2478</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -10624,7 +10624,7 @@
         <v>43668</v>
       </c>
       <c r="E43" t="n">
-        <v>2462</v>
+        <v>2467</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -10650,7 +10650,7 @@
         <v>43670</v>
       </c>
       <c r="E44" t="n">
-        <v>2460</v>
+        <v>2465</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -10676,7 +10676,7 @@
         <v>43678</v>
       </c>
       <c r="E45" t="n">
-        <v>2452</v>
+        <v>2457</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -10702,7 +10702,7 @@
         <v>43687</v>
       </c>
       <c r="E46" t="n">
-        <v>2443</v>
+        <v>2448</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -10728,7 +10728,7 @@
         <v>43691</v>
       </c>
       <c r="E47" t="n">
-        <v>2439</v>
+        <v>2444</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -10754,7 +10754,7 @@
         <v>43760</v>
       </c>
       <c r="E48" t="n">
-        <v>2370</v>
+        <v>2375</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -10780,7 +10780,7 @@
         <v>43776</v>
       </c>
       <c r="E49" t="n">
-        <v>2354</v>
+        <v>2359</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -10806,7 +10806,7 @@
         <v>43806</v>
       </c>
       <c r="E50" t="n">
-        <v>2324</v>
+        <v>2329</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -10832,7 +10832,7 @@
         <v>43823</v>
       </c>
       <c r="E51" t="n">
-        <v>2307</v>
+        <v>2312</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -10858,7 +10858,7 @@
         <v>43879</v>
       </c>
       <c r="E52" t="n">
-        <v>2251</v>
+        <v>2256</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -10884,7 +10884,7 @@
         <v>43914</v>
       </c>
       <c r="E53" t="n">
-        <v>2216</v>
+        <v>2221</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -10910,7 +10910,7 @@
         <v>43964</v>
       </c>
       <c r="E54" t="n">
-        <v>2166</v>
+        <v>2171</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -10936,7 +10936,7 @@
         <v>44005</v>
       </c>
       <c r="E55" t="n">
-        <v>2125</v>
+        <v>2130</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -10962,7 +10962,7 @@
         <v>44035</v>
       </c>
       <c r="E56" t="n">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -10988,7 +10988,7 @@
         <v>44037</v>
       </c>
       <c r="E57" t="n">
-        <v>2093</v>
+        <v>2098</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -11014,7 +11014,7 @@
         <v>44054</v>
       </c>
       <c r="E58" t="n">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -11040,7 +11040,7 @@
         <v>44071</v>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -11066,7 +11066,7 @@
         <v>44071</v>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -11092,7 +11092,7 @@
         <v>44071</v>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>2064</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -11118,7 +11118,7 @@
         <v>44114</v>
       </c>
       <c r="E62" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -11144,7 +11144,7 @@
         <v>44151</v>
       </c>
       <c r="E63" t="n">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -11170,7 +11170,7 @@
         <v>44212</v>
       </c>
       <c r="E64" t="n">
-        <v>1918</v>
+        <v>1923</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -11196,7 +11196,7 @@
         <v>44255</v>
       </c>
       <c r="E65" t="n">
-        <v>1875</v>
+        <v>1880</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -11222,7 +11222,7 @@
         <v>44258</v>
       </c>
       <c r="E66" t="n">
-        <v>1872</v>
+        <v>1877</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -11248,7 +11248,7 @@
         <v>44285</v>
       </c>
       <c r="E67" t="n">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -11274,7 +11274,7 @@
         <v>44286</v>
       </c>
       <c r="E68" t="n">
-        <v>1844</v>
+        <v>1849</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -11300,7 +11300,7 @@
         <v>44288</v>
       </c>
       <c r="E69" t="n">
-        <v>1842</v>
+        <v>1847</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -11326,7 +11326,7 @@
         <v>44297</v>
       </c>
       <c r="E70" t="n">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -11352,7 +11352,7 @@
         <v>44297</v>
       </c>
       <c r="E71" t="n">
-        <v>1833</v>
+        <v>1838</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -11378,7 +11378,7 @@
         <v>44327</v>
       </c>
       <c r="E72" t="n">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -11404,7 +11404,7 @@
         <v>44335</v>
       </c>
       <c r="E73" t="n">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -11430,7 +11430,7 @@
         <v>44341</v>
       </c>
       <c r="E74" t="n">
-        <v>1789</v>
+        <v>1794</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -11456,7 +11456,7 @@
         <v>44352</v>
       </c>
       <c r="E75" t="n">
-        <v>1778</v>
+        <v>1783</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -11482,7 +11482,7 @@
         <v>44384</v>
       </c>
       <c r="E76" t="n">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -11508,7 +11508,7 @@
         <v>44385</v>
       </c>
       <c r="E77" t="n">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -11534,7 +11534,7 @@
         <v>44392</v>
       </c>
       <c r="E78" t="n">
-        <v>1738</v>
+        <v>1743</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -11560,7 +11560,7 @@
         <v>44394</v>
       </c>
       <c r="E79" t="n">
-        <v>1736</v>
+        <v>1741</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -11586,7 +11586,7 @@
         <v>44442</v>
       </c>
       <c r="E80" t="n">
-        <v>1688</v>
+        <v>1693</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -11612,7 +11612,7 @@
         <v>44468</v>
       </c>
       <c r="E81" t="n">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         <v>44486</v>
       </c>
       <c r="E82" t="n">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -11664,7 +11664,7 @@
         <v>44512</v>
       </c>
       <c r="E83" t="n">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -11690,7 +11690,7 @@
         <v>44535</v>
       </c>
       <c r="E84" t="n">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -11716,7 +11716,7 @@
         <v>44553</v>
       </c>
       <c r="E85" t="n">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -11742,7 +11742,7 @@
         <v>44554</v>
       </c>
       <c r="E86" t="n">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -11768,7 +11768,7 @@
         <v>44601</v>
       </c>
       <c r="E87" t="n">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -11794,7 +11794,7 @@
         <v>44617</v>
       </c>
       <c r="E88" t="n">
-        <v>1513</v>
+        <v>1518</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
@@ -11820,7 +11820,7 @@
         <v>44636</v>
       </c>
       <c r="E89" t="n">
-        <v>1494</v>
+        <v>1499</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
@@ -11846,7 +11846,7 @@
         <v>44637</v>
       </c>
       <c r="E90" t="n">
-        <v>1493</v>
+        <v>1498</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
@@ -11872,7 +11872,7 @@
         <v>44639</v>
       </c>
       <c r="E91" t="n">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
@@ -11898,7 +11898,7 @@
         <v>44645</v>
       </c>
       <c r="E92" t="n">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
@@ -11924,7 +11924,7 @@
         <v>44681</v>
       </c>
       <c r="E93" t="n">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -11950,7 +11950,7 @@
         <v>44717</v>
       </c>
       <c r="E94" t="n">
-        <v>1413</v>
+        <v>1418</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
@@ -11976,7 +11976,7 @@
         <v>44730</v>
       </c>
       <c r="E95" t="n">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="F95" t="b">
         <v>1</v>
@@ -12002,7 +12002,7 @@
         <v>44732</v>
       </c>
       <c r="E96" t="n">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
@@ -12028,7 +12028,7 @@
         <v>44748</v>
       </c>
       <c r="E97" t="n">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
@@ -12054,7 +12054,7 @@
         <v>44763</v>
       </c>
       <c r="E98" t="n">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
@@ -12080,7 +12080,7 @@
         <v>44767</v>
       </c>
       <c r="E99" t="n">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
@@ -12106,7 +12106,7 @@
         <v>44794</v>
       </c>
       <c r="E100" t="n">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -12132,7 +12132,7 @@
         <v>44794</v>
       </c>
       <c r="E101" t="n">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
@@ -12158,7 +12158,7 @@
         <v>44814</v>
       </c>
       <c r="E102" t="n">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
@@ -12184,7 +12184,7 @@
         <v>44818</v>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
@@ -12210,7 +12210,7 @@
         <v>44819</v>
       </c>
       <c r="E104" t="n">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -12236,7 +12236,7 @@
         <v>44842</v>
       </c>
       <c r="E105" t="n">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
@@ -12262,7 +12262,7 @@
         <v>44856</v>
       </c>
       <c r="E106" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
@@ -12288,7 +12288,7 @@
         <v>44859</v>
       </c>
       <c r="E107" t="n">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -12314,7 +12314,7 @@
         <v>44865</v>
       </c>
       <c r="E108" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
@@ -12340,7 +12340,7 @@
         <v>44868</v>
       </c>
       <c r="E109" t="n">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
@@ -12366,7 +12366,7 @@
         <v>44869</v>
       </c>
       <c r="E110" t="n">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
@@ -12392,7 +12392,7 @@
         <v>44873</v>
       </c>
       <c r="E111" t="n">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
@@ -12418,7 +12418,7 @@
         <v>44878</v>
       </c>
       <c r="E112" t="n">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
@@ -12444,7 +12444,7 @@
         <v>44883</v>
       </c>
       <c r="E113" t="n">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="F113" t="b">
         <v>1</v>
@@ -12470,7 +12470,7 @@
         <v>44885</v>
       </c>
       <c r="E114" t="n">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
@@ -12496,7 +12496,7 @@
         <v>44904</v>
       </c>
       <c r="E115" t="n">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
@@ -12522,7 +12522,7 @@
         <v>44910</v>
       </c>
       <c r="E116" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="F116" t="b">
         <v>1</v>
@@ -12548,7 +12548,7 @@
         <v>44911</v>
       </c>
       <c r="E117" t="n">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
@@ -12574,7 +12574,7 @@
         <v>44913</v>
       </c>
       <c r="E118" t="n">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
@@ -12600,7 +12600,7 @@
         <v>44915</v>
       </c>
       <c r="E119" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
@@ -12626,7 +12626,7 @@
         <v>44917</v>
       </c>
       <c r="E120" t="n">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
@@ -12652,7 +12652,7 @@
         <v>44981</v>
       </c>
       <c r="E121" t="n">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
@@ -12678,7 +12678,7 @@
         <v>44996</v>
       </c>
       <c r="E122" t="n">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
@@ -12704,7 +12704,7 @@
         <v>45005</v>
       </c>
       <c r="E123" t="n">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
@@ -12730,7 +12730,7 @@
         <v>45006</v>
       </c>
       <c r="E124" t="n">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
@@ -12756,7 +12756,7 @@
         <v>45034</v>
       </c>
       <c r="E125" t="n">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
@@ -12782,7 +12782,7 @@
         <v>45039</v>
       </c>
       <c r="E126" t="n">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
@@ -12808,7 +12808,7 @@
         <v>45041</v>
       </c>
       <c r="E127" t="n">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
@@ -12834,7 +12834,7 @@
         <v>45048</v>
       </c>
       <c r="E128" t="n">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
@@ -12860,7 +12860,7 @@
         <v>45056</v>
       </c>
       <c r="E129" t="n">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
@@ -12886,7 +12886,7 @@
         <v>45060</v>
       </c>
       <c r="E130" t="n">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
@@ -12912,7 +12912,7 @@
         <v>45065</v>
       </c>
       <c r="E131" t="n">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
@@ -12938,7 +12938,7 @@
         <v>45067</v>
       </c>
       <c r="E132" t="n">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
@@ -12964,7 +12964,7 @@
         <v>45072</v>
       </c>
       <c r="E133" t="n">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
@@ -12990,7 +12990,7 @@
         <v>45090</v>
       </c>
       <c r="E134" t="n">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="F134" t="b">
         <v>1</v>
@@ -13016,7 +13016,7 @@
         <v>45102</v>
       </c>
       <c r="E135" t="n">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
@@ -13042,7 +13042,7 @@
         <v>45139</v>
       </c>
       <c r="E136" t="n">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="F136" t="b">
         <v>1</v>
@@ -13068,7 +13068,7 @@
         <v>45147</v>
       </c>
       <c r="E137" t="n">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
@@ -13094,7 +13094,7 @@
         <v>45151</v>
       </c>
       <c r="E138" t="n">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
@@ -13120,7 +13120,7 @@
         <v>45164</v>
       </c>
       <c r="E139" t="n">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
@@ -13146,7 +13146,7 @@
         <v>45166</v>
       </c>
       <c r="E140" t="n">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
@@ -13172,7 +13172,7 @@
         <v>45180</v>
       </c>
       <c r="E141" t="n">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
@@ -13198,7 +13198,7 @@
         <v>45182</v>
       </c>
       <c r="E142" t="n">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
@@ -13224,7 +13224,7 @@
         <v>45186</v>
       </c>
       <c r="E143" t="n">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
@@ -13250,7 +13250,7 @@
         <v>45204</v>
       </c>
       <c r="E144" t="n">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
@@ -13276,7 +13276,7 @@
         <v>45207</v>
       </c>
       <c r="E145" t="n">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
@@ -13302,7 +13302,7 @@
         <v>45219</v>
       </c>
       <c r="E146" t="n">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
@@ -13328,7 +13328,7 @@
         <v>45248</v>
       </c>
       <c r="E147" t="n">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F147" t="b">
         <v>1</v>
@@ -13354,7 +13354,7 @@
         <v>45260</v>
       </c>
       <c r="E148" t="n">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -13380,7 +13380,7 @@
         <v>45278</v>
       </c>
       <c r="E149" t="n">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
@@ -13406,7 +13406,7 @@
         <v>45279</v>
       </c>
       <c r="E150" t="n">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
@@ -13432,7 +13432,7 @@
         <v>45285</v>
       </c>
       <c r="E151" t="n">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -13458,7 +13458,7 @@
         <v>45309</v>
       </c>
       <c r="E152" t="n">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="F152" t="b">
         <v>1</v>
@@ -13484,7 +13484,7 @@
         <v>45322</v>
       </c>
       <c r="E153" t="n">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="F153" t="b">
         <v>1</v>
@@ -13510,7 +13510,7 @@
         <v>45334</v>
       </c>
       <c r="E154" t="n">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F154" t="b">
         <v>1</v>
@@ -13536,7 +13536,7 @@
         <v>45336</v>
       </c>
       <c r="E155" t="n">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F155" t="b">
         <v>1</v>
@@ -13562,7 +13562,7 @@
         <v>45346</v>
       </c>
       <c r="E156" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="F156" t="b">
         <v>1</v>
@@ -13588,7 +13588,7 @@
         <v>45347</v>
       </c>
       <c r="E157" t="n">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="F157" t="b">
         <v>1</v>
@@ -13614,7 +13614,7 @@
         <v>45365</v>
       </c>
       <c r="E158" t="n">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="F158" t="b">
         <v>1</v>
@@ -13640,7 +13640,7 @@
         <v>45380</v>
       </c>
       <c r="E159" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
@@ -13666,7 +13666,7 @@
         <v>45382</v>
       </c>
       <c r="E160" t="n">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
@@ -13692,7 +13692,7 @@
         <v>45398</v>
       </c>
       <c r="E161" t="n">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="F161" t="b">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         <v>45400</v>
       </c>
       <c r="E162" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="F162" t="b">
         <v>1</v>
@@ -13744,7 +13744,7 @@
         <v>45401</v>
       </c>
       <c r="E163" t="n">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="F163" t="b">
         <v>1</v>
@@ -13770,7 +13770,7 @@
         <v>45404</v>
       </c>
       <c r="E164" t="n">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="F164" t="b">
         <v>1</v>
@@ -13796,7 +13796,7 @@
         <v>45408</v>
       </c>
       <c r="E165" t="n">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
@@ -13822,7 +13822,7 @@
         <v>45425</v>
       </c>
       <c r="E166" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
@@ -13848,7 +13848,7 @@
         <v>45429</v>
       </c>
       <c r="E167" t="n">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="F167" t="b">
         <v>1</v>
@@ -13874,7 +13874,7 @@
         <v>45431</v>
       </c>
       <c r="E168" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F168" t="b">
         <v>1</v>
@@ -13900,7 +13900,7 @@
         <v>45435</v>
       </c>
       <c r="E169" t="n">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="F169" t="b">
         <v>1</v>
@@ -13926,7 +13926,7 @@
         <v>45449</v>
       </c>
       <c r="E170" t="n">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="F170" t="b">
         <v>1</v>
@@ -13952,7 +13952,7 @@
         <v>45459</v>
       </c>
       <c r="E171" t="n">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="F171" t="b">
         <v>1</v>
@@ -13978,7 +13978,7 @@
         <v>45470</v>
       </c>
       <c r="E172" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="F172" t="b">
         <v>1</v>
@@ -14004,7 +14004,7 @@
         <v>45479</v>
       </c>
       <c r="E173" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="F173" t="b">
         <v>1</v>
@@ -14030,7 +14030,7 @@
         <v>45482</v>
       </c>
       <c r="E174" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="F174" t="b">
         <v>1</v>
@@ -14056,7 +14056,7 @@
         <v>45489</v>
       </c>
       <c r="E175" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="F175" t="b">
         <v>1</v>
@@ -14082,7 +14082,7 @@
         <v>45490</v>
       </c>
       <c r="E176" t="n">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="F176" t="b">
         <v>1</v>
@@ -14108,7 +14108,7 @@
         <v>45499</v>
       </c>
       <c r="E177" t="n">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="F177" t="b">
         <v>1</v>
@@ -14134,7 +14134,7 @@
         <v>45505</v>
       </c>
       <c r="E178" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F178" t="b">
         <v>1</v>
@@ -14160,7 +14160,7 @@
         <v>45514</v>
       </c>
       <c r="E179" t="n">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F179" t="b">
         <v>1</v>
@@ -14186,7 +14186,7 @@
         <v>45527</v>
       </c>
       <c r="E180" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="F180" t="b">
         <v>1</v>
@@ -14212,7 +14212,7 @@
         <v>45532</v>
       </c>
       <c r="E181" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="F181" t="b">
         <v>1</v>
@@ -14238,7 +14238,7 @@
         <v>45535</v>
       </c>
       <c r="E182" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
@@ -14264,7 +14264,7 @@
         <v>45535</v>
       </c>
       <c r="E183" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F183" t="b">
         <v>1</v>
@@ -14290,7 +14290,7 @@
         <v>45545</v>
       </c>
       <c r="E184" t="n">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F184" t="b">
         <v>1</v>
@@ -14316,7 +14316,7 @@
         <v>45547</v>
       </c>
       <c r="E185" t="n">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F185" t="b">
         <v>1</v>
@@ -14342,7 +14342,7 @@
         <v>45566</v>
       </c>
       <c r="E186" t="n">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
@@ -14368,7 +14368,7 @@
         <v>45573</v>
       </c>
       <c r="E187" t="n">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
@@ -14394,7 +14394,7 @@
         <v>45593</v>
       </c>
       <c r="E188" t="n">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F188" t="b">
         <v>1</v>
@@ -14420,7 +14420,7 @@
         <v>45599</v>
       </c>
       <c r="E189" t="n">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -14446,7 +14446,7 @@
         <v>45616</v>
       </c>
       <c r="E190" t="n">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -14472,7 +14472,7 @@
         <v>45621</v>
       </c>
       <c r="E191" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F191" t="b">
         <v>1</v>
@@ -14498,7 +14498,7 @@
         <v>45630</v>
       </c>
       <c r="E192" t="n">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F192" t="b">
         <v>1</v>
@@ -14524,7 +14524,7 @@
         <v>45649</v>
       </c>
       <c r="E193" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F193" t="b">
         <v>1</v>
@@ -14550,7 +14550,7 @@
         <v>45651</v>
       </c>
       <c r="E194" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F194" t="b">
         <v>1</v>
@@ -14576,7 +14576,7 @@
         <v>45672</v>
       </c>
       <c r="E195" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -14602,7 +14602,7 @@
         <v>45716</v>
       </c>
       <c r="E196" t="n">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
@@ -14628,7 +14628,7 @@
         <v>45718</v>
       </c>
       <c r="E197" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -14654,7 +14654,7 @@
         <v>45719</v>
       </c>
       <c r="E198" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -14680,7 +14680,7 @@
         <v>45723</v>
       </c>
       <c r="E199" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -14706,7 +14706,7 @@
         <v>45727</v>
       </c>
       <c r="E200" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -14732,7 +14732,7 @@
         <v>45729</v>
       </c>
       <c r="E201" t="n">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -14758,7 +14758,7 @@
         <v>45742</v>
       </c>
       <c r="E202" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -14784,7 +14784,7 @@
         <v>45753</v>
       </c>
       <c r="E203" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -14810,7 +14810,7 @@
         <v>45757</v>
       </c>
       <c r="E204" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F204" t="b">
         <v>1</v>
@@ -14836,10 +14836,10 @@
         <v>45767</v>
       </c>
       <c r="E205" t="n">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -14862,10 +14862,10 @@
         <v>45768</v>
       </c>
       <c r="E206" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -14888,7 +14888,7 @@
         <v>45773</v>
       </c>
       <c r="E207" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F207" t="b">
         <v>0</v>
@@ -14914,7 +14914,7 @@
         <v>45777</v>
       </c>
       <c r="E208" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F208" t="b">
         <v>0</v>
@@ -14940,7 +14940,7 @@
         <v>45778</v>
       </c>
       <c r="E209" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F209" t="b">
         <v>0</v>
@@ -14966,7 +14966,7 @@
         <v>45780</v>
       </c>
       <c r="E210" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F210" t="b">
         <v>0</v>
@@ -14992,7 +14992,7 @@
         <v>45786</v>
       </c>
       <c r="E211" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F211" t="b">
         <v>0</v>
@@ -15018,7 +15018,7 @@
         <v>45788</v>
       </c>
       <c r="E212" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F212" t="b">
         <v>0</v>
@@ -15044,7 +15044,7 @@
         <v>45802</v>
       </c>
       <c r="E213" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F213" t="b">
         <v>0</v>
@@ -15070,7 +15070,7 @@
         <v>45809</v>
       </c>
       <c r="E214" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F214" t="b">
         <v>0</v>
@@ -15096,7 +15096,7 @@
         <v>45819</v>
       </c>
       <c r="E215" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F215" t="b">
         <v>0</v>
@@ -15122,7 +15122,7 @@
         <v>45830</v>
       </c>
       <c r="E216" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F216" t="b">
         <v>0</v>
@@ -15148,7 +15148,7 @@
         <v>45833</v>
       </c>
       <c r="E217" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F217" t="b">
         <v>0</v>
@@ -15174,7 +15174,7 @@
         <v>45836</v>
       </c>
       <c r="E218" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F218" t="b">
         <v>0</v>
@@ -15200,7 +15200,7 @@
         <v>45838</v>
       </c>
       <c r="E219" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F219" t="b">
         <v>0</v>
@@ -15226,7 +15226,7 @@
         <v>45845</v>
       </c>
       <c r="E220" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F220" t="b">
         <v>0</v>
@@ -15252,7 +15252,7 @@
         <v>45873</v>
       </c>
       <c r="E221" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F221" t="b">
         <v>0</v>
@@ -15278,7 +15278,7 @@
         <v>45873</v>
       </c>
       <c r="E222" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F222" t="b">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>45882</v>
       </c>
       <c r="E223" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F223" t="b">
         <v>0</v>
@@ -15330,7 +15330,7 @@
         <v>45890</v>
       </c>
       <c r="E224" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F224" t="b">
         <v>0</v>
@@ -15356,7 +15356,7 @@
         <v>45904</v>
       </c>
       <c r="E225" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F225" t="b">
         <v>0</v>
@@ -15382,7 +15382,7 @@
         <v>45924</v>
       </c>
       <c r="E226" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F226" t="b">
         <v>0</v>
@@ -15408,7 +15408,7 @@
         <v>45929</v>
       </c>
       <c r="E227" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F227" t="b">
         <v>0</v>
@@ -15434,7 +15434,7 @@
         <v>45929</v>
       </c>
       <c r="E228" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F228" t="b">
         <v>0</v>
@@ -15460,7 +15460,7 @@
         <v>45931</v>
       </c>
       <c r="E229" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F229" t="b">
         <v>0</v>
@@ -15486,7 +15486,7 @@
         <v>45932</v>
       </c>
       <c r="E230" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F230" t="b">
         <v>0</v>
@@ -15512,7 +15512,7 @@
         <v>45950</v>
       </c>
       <c r="E231" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F231" t="b">
         <v>0</v>
@@ -15538,7 +15538,7 @@
         <v>45953</v>
       </c>
       <c r="E232" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F232" t="b">
         <v>0</v>
@@ -15564,7 +15564,7 @@
         <v>45957</v>
       </c>
       <c r="E233" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F233" t="b">
         <v>0</v>
@@ -15590,7 +15590,7 @@
         <v>45965</v>
       </c>
       <c r="E234" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F234" t="b">
         <v>0</v>
@@ -15616,7 +15616,7 @@
         <v>45967</v>
       </c>
       <c r="E235" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F235" t="b">
         <v>0</v>
@@ -15642,7 +15642,7 @@
         <v>45968</v>
       </c>
       <c r="E236" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F236" t="b">
         <v>0</v>
@@ -15668,7 +15668,7 @@
         <v>45973</v>
       </c>
       <c r="E237" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F237" t="b">
         <v>0</v>
@@ -15694,7 +15694,7 @@
         <v>45977</v>
       </c>
       <c r="E238" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F238" t="b">
         <v>0</v>
@@ -15720,7 +15720,7 @@
         <v>45994</v>
       </c>
       <c r="E239" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F239" t="b">
         <v>0</v>
@@ -15746,7 +15746,7 @@
         <v>45999</v>
       </c>
       <c r="E240" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F240" t="b">
         <v>0</v>
@@ -15772,7 +15772,7 @@
         <v>45999</v>
       </c>
       <c r="E241" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F241" t="b">
         <v>0</v>
@@ -15798,7 +15798,7 @@
         <v>46000</v>
       </c>
       <c r="E242" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F242" t="b">
         <v>0</v>
@@ -15824,7 +15824,7 @@
         <v>46000</v>
       </c>
       <c r="E243" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F243" t="b">
         <v>0</v>
@@ -15850,7 +15850,7 @@
         <v>46007</v>
       </c>
       <c r="E244" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F244" t="b">
         <v>0</v>
@@ -15876,7 +15876,7 @@
         <v>46009</v>
       </c>
       <c r="E245" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F245" t="b">
         <v>0</v>
@@ -15902,7 +15902,7 @@
         <v>46009</v>
       </c>
       <c r="E246" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F246" t="b">
         <v>0</v>
@@ -15928,7 +15928,7 @@
         <v>46013</v>
       </c>
       <c r="E247" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F247" t="b">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46014</v>
       </c>
       <c r="E248" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F248" t="b">
         <v>0</v>
@@ -15980,7 +15980,7 @@
         <v>46017</v>
       </c>
       <c r="E249" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F249" t="b">
         <v>0</v>
@@ -16006,7 +16006,7 @@
         <v>46017</v>
       </c>
       <c r="E250" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F250" t="b">
         <v>0</v>
@@ -16032,7 +16032,7 @@
         <v>46021</v>
       </c>
       <c r="E251" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F251" t="b">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>46021</v>
       </c>
       <c r="E252" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F252" t="b">
         <v>0</v>
@@ -16084,7 +16084,7 @@
         <v>46030</v>
       </c>
       <c r="E253" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F253" t="b">
         <v>0</v>
@@ -16110,7 +16110,7 @@
         <v>46034</v>
       </c>
       <c r="E254" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F254" t="b">
         <v>0</v>
@@ -16136,7 +16136,7 @@
         <v>46036</v>
       </c>
       <c r="E255" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F255" t="b">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>46042</v>
       </c>
       <c r="E256" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F256" t="b">
         <v>0</v>
@@ -16188,7 +16188,7 @@
         <v>46051</v>
       </c>
       <c r="E257" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F257" t="b">
         <v>0</v>
@@ -16214,7 +16214,7 @@
         <v>46052</v>
       </c>
       <c r="E258" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F258" t="b">
         <v>0</v>
@@ -16240,7 +16240,7 @@
         <v>46055</v>
       </c>
       <c r="E259" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F259" t="b">
         <v>0</v>
@@ -16266,7 +16266,7 @@
         <v>46056</v>
       </c>
       <c r="E260" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F260" t="b">
         <v>0</v>
@@ -16292,7 +16292,7 @@
         <v>46059</v>
       </c>
       <c r="E261" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F261" t="b">
         <v>0</v>
@@ -16318,7 +16318,7 @@
         <v>46064</v>
       </c>
       <c r="E262" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F262" t="b">
         <v>0</v>
@@ -16344,7 +16344,7 @@
         <v>46066</v>
       </c>
       <c r="E263" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F263" t="b">
         <v>0</v>
@@ -16370,7 +16370,7 @@
         <v>46073</v>
       </c>
       <c r="E264" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F264" t="b">
         <v>0</v>
@@ -16396,7 +16396,7 @@
         <v>46073</v>
       </c>
       <c r="E265" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F265" t="b">
         <v>0</v>
@@ -16422,7 +16422,7 @@
         <v>46080</v>
       </c>
       <c r="E266" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F266" t="b">
         <v>0</v>
@@ -16448,7 +16448,7 @@
         <v>46080</v>
       </c>
       <c r="E267" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F267" t="b">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>46082</v>
       </c>
       <c r="E268" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F268" t="b">
         <v>0</v>
@@ -16500,7 +16500,7 @@
         <v>46082</v>
       </c>
       <c r="E269" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F269" t="b">
         <v>0</v>
@@ -16526,7 +16526,7 @@
         <v>46083</v>
       </c>
       <c r="E270" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F270" t="b">
         <v>0</v>
@@ -16552,7 +16552,7 @@
         <v>46085</v>
       </c>
       <c r="E271" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F271" t="b">
         <v>0</v>
@@ -16578,7 +16578,7 @@
         <v>46127</v>
       </c>
       <c r="E272" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F272" t="b">
         <v>0</v>
@@ -33788,7 +33788,7 @@
         <v>46167</v>
       </c>
       <c r="E989" t="n">
-        <v>-37</v>
+        <v>-32</v>
       </c>
       <c r="F989" t="b">
         <v>0</v>
@@ -33814,7 +33814,7 @@
         <v>46201</v>
       </c>
       <c r="E990" t="n">
-        <v>-71</v>
+        <v>-66</v>
       </c>
       <c r="F990" t="b">
         <v>0</v>
@@ -33840,7 +33840,7 @@
         <v>46234</v>
       </c>
       <c r="E991" t="n">
-        <v>-104</v>
+        <v>-99</v>
       </c>
       <c r="F991" t="b">
         <v>0</v>
@@ -33866,7 +33866,7 @@
         <v>46242</v>
       </c>
       <c r="E992" t="n">
-        <v>-112</v>
+        <v>-107</v>
       </c>
       <c r="F992" t="b">
         <v>0</v>
@@ -33892,7 +33892,7 @@
         <v>46270</v>
       </c>
       <c r="E993" t="n">
-        <v>-140</v>
+        <v>-135</v>
       </c>
       <c r="F993" t="b">
         <v>0</v>
@@ -33918,7 +33918,7 @@
         <v>46281</v>
       </c>
       <c r="E994" t="n">
-        <v>-151</v>
+        <v>-146</v>
       </c>
       <c r="F994" t="b">
         <v>0</v>
@@ -33944,7 +33944,7 @@
         <v>46292</v>
       </c>
       <c r="E995" t="n">
-        <v>-162</v>
+        <v>-157</v>
       </c>
       <c r="F995" t="b">
         <v>0</v>
@@ -33970,7 +33970,7 @@
         <v>46295</v>
       </c>
       <c r="E996" t="n">
-        <v>-165</v>
+        <v>-160</v>
       </c>
       <c r="F996" t="b">
         <v>0</v>
@@ -33996,7 +33996,7 @@
         <v>46295</v>
       </c>
       <c r="E997" t="n">
-        <v>-165</v>
+        <v>-160</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -34022,7 +34022,7 @@
         <v>46298</v>
       </c>
       <c r="E998" t="n">
-        <v>-168</v>
+        <v>-163</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -34048,7 +34048,7 @@
         <v>46305</v>
       </c>
       <c r="E999" t="n">
-        <v>-175</v>
+        <v>-170</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -34074,7 +34074,7 @@
         <v>46312</v>
       </c>
       <c r="E1000" t="n">
-        <v>-182</v>
+        <v>-177</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -34100,7 +34100,7 @@
         <v>46315</v>
       </c>
       <c r="E1001" t="n">
-        <v>-185</v>
+        <v>-180</v>
       </c>
       <c r="F1001" t="b">
         <v>0</v>
